--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.49209</v>
+        <v>16.75505</v>
       </c>
       <c r="D2" t="n">
-        <v>16.11992</v>
+        <v>16.40297</v>
       </c>
       <c r="E2" t="n">
-        <v>16.6215</v>
+        <v>16.51798</v>
       </c>
       <c r="F2" t="n">
-        <v>41.4752</v>
+        <v>42.63876</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05001</v>
+        <v>0.05078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77753</v>
+        <v>1.81794</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.74783</v>
+        <v>16.75572</v>
       </c>
       <c r="D3" t="n">
-        <v>16.50384</v>
+        <v>16.4015</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62176</v>
+        <v>16.67578</v>
       </c>
       <c r="F3" t="n">
-        <v>41.72624</v>
+        <v>42.05318</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05008</v>
+        <v>0.05001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82557</v>
+        <v>1.81306</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.58461</v>
+        <v>17.01391</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6766</v>
+        <v>16.33455</v>
       </c>
       <c r="E4" t="n">
-        <v>16.30895</v>
+        <v>16.55722</v>
       </c>
       <c r="F4" t="n">
-        <v>41.76784</v>
+        <v>41.99238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05052</v>
+        <v>0.05053</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78774</v>
+        <v>1.75232</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.52564</v>
+        <v>16.78109</v>
       </c>
       <c r="D6" t="n">
-        <v>15.53967</v>
+        <v>15.99486</v>
       </c>
       <c r="E6" t="n">
-        <v>16.54054</v>
+        <v>16.18097</v>
       </c>
       <c r="F6" t="n">
-        <v>21.97431</v>
+        <v>21.20993</v>
       </c>
       <c r="G6" t="n">
-        <v>34.32798</v>
+        <v>34.19296</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.34188</v>
+        <v>16.65039</v>
       </c>
       <c r="D7" t="n">
-        <v>15.86758</v>
+        <v>15.87722</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4713</v>
+        <v>16.21706</v>
       </c>
       <c r="F7" t="n">
-        <v>21.63039</v>
+        <v>21.66421</v>
       </c>
       <c r="G7" t="n">
-        <v>34.06873</v>
+        <v>34.07854</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.64835</v>
+        <v>16.46312</v>
       </c>
       <c r="D8" t="n">
-        <v>16.04859</v>
+        <v>16.01853</v>
       </c>
       <c r="E8" t="n">
-        <v>16.26904</v>
+        <v>16.13317</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79831</v>
+        <v>21.53016</v>
       </c>
       <c r="G8" t="n">
-        <v>34.75602</v>
+        <v>34.08049</v>
       </c>
     </row>
   </sheetData>
